--- a/grupos/3APM - Estadisticos 20231.xlsx
+++ b/grupos/3APM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -200,21 +200,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -230,46 +230,55 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>CERON</t>
   </si>
   <si>
     <t>VICENTE</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>AVALOS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>QUINTANA</t>
   </si>
   <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>EDUARDO EMER</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>CRISTIAN</t>
@@ -780,19 +789,19 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -816,10 +825,10 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -857,19 +866,19 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -893,19 +902,19 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -934,19 +943,19 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -970,16 +979,16 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>9</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1011,19 +1020,19 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1050,16 +1059,16 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>10</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1088,19 +1097,19 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1127,13 +1136,13 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1165,19 +1174,19 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1201,19 +1210,19 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1242,19 +1251,19 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1278,7 +1287,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1319,19 +1328,19 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1355,19 +1364,19 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1396,19 +1405,19 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1432,16 +1441,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>10</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1473,19 +1482,19 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1509,16 +1518,16 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1550,19 +1559,19 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1586,13 +1595,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1627,19 +1636,19 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1669,10 +1678,10 @@
         <v>5</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1704,19 +1713,19 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1781,19 +1790,19 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1820,16 +1829,16 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -1858,19 +1867,19 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -1894,19 +1903,19 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>9</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -1935,19 +1944,19 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -1971,16 +1980,16 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2012,19 +2021,19 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2048,7 +2057,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2089,19 +2098,19 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2125,7 +2134,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2134,7 +2143,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2166,19 +2175,19 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2202,7 +2211,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2211,10 +2220,10 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2243,19 +2252,19 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2279,19 +2288,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>9</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2320,19 +2329,19 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2356,19 +2365,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>10</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2397,19 +2406,19 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2433,19 +2442,19 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2474,19 +2483,19 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2510,16 +2519,16 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>10</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2551,19 +2560,19 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2587,16 +2596,16 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>7</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2628,19 +2637,19 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2664,7 +2673,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>9</v>
@@ -2673,7 +2682,7 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2705,19 +2714,19 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2750,7 +2759,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -2782,19 +2791,19 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2818,16 +2827,16 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -2859,19 +2868,19 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -2901,13 +2910,13 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2936,19 +2945,19 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -2972,19 +2981,19 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3013,19 +3022,19 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3049,19 +3058,19 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>8</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3090,19 +3099,19 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3126,19 +3135,19 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>7</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3167,19 +3176,19 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3206,7 +3215,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3244,19 +3253,19 @@
         <v>8</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3280,7 +3289,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U36">
         <v>8</v>
@@ -3289,10 +3298,10 @@
         <v>9</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3321,19 +3330,19 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3357,13 +3366,13 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3395,22 +3404,22 @@
         <v>5</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3434,13 +3443,13 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3449,7 +3458,7 @@
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3475,19 +3484,19 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3511,19 +3520,19 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>5</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>6</v>
@@ -3721,7 +3730,7 @@
         <v>81</v>
       </c>
       <c r="H5">
-        <v>92.5</v>
+        <v>96.3</v>
       </c>
       <c r="I5">
         <v>88.90000000000001</v>
@@ -3730,7 +3739,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -3739,7 +3748,7 @@
         <v>81</v>
       </c>
       <c r="N5">
-        <v>92.5</v>
+        <v>96.3</v>
       </c>
       <c r="O5">
         <v>88.90000000000001</v>
@@ -3748,7 +3757,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -3780,7 +3789,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>97.5</v>
+        <v>98.8</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -3798,7 +3807,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>97.5</v>
+        <v>98.8</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3839,7 +3848,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -3857,7 +3866,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3898,7 +3907,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -3916,7 +3925,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -3957,7 +3966,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>92.5</v>
+        <v>91.3</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -3966,7 +3975,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -3975,7 +3984,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>92.5</v>
+        <v>91.3</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3984,7 +3993,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4134,7 +4143,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -4152,7 +4161,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4193,16 +4202,16 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="I13">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -4211,16 +4220,16 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="O13">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4252,16 +4261,16 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="I14">
-        <v>91.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4270,16 +4279,16 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="O14">
-        <v>91.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4311,16 +4320,16 @@
         <v>100</v>
       </c>
       <c r="H15">
+        <v>92.5</v>
+      </c>
+      <c r="I15">
+        <v>93.3</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
         <v>95</v>
-      </c>
-      <c r="I15">
-        <v>97.8</v>
-      </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
-      <c r="K15">
-        <v>90</v>
       </c>
       <c r="L15">
         <v>62.5</v>
@@ -4329,16 +4338,16 @@
         <v>100</v>
       </c>
       <c r="N15">
+        <v>92.5</v>
+      </c>
+      <c r="O15">
+        <v>93.3</v>
+      </c>
+      <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
         <v>95</v>
-      </c>
-      <c r="O15">
-        <v>97.8</v>
-      </c>
-      <c r="P15">
-        <v>100</v>
-      </c>
-      <c r="Q15">
-        <v>90</v>
       </c>
       <c r="R15">
         <v>62.5</v>
@@ -4370,37 +4379,37 @@
         <v>81</v>
       </c>
       <c r="H16">
-        <v>87.5</v>
+        <v>66.3</v>
       </c>
       <c r="I16">
         <v>100</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K16">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M16">
         <v>81</v>
       </c>
       <c r="N16">
-        <v>87.5</v>
+        <v>66.3</v>
       </c>
       <c r="O16">
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q16">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="S16">
         <v>81</v>
@@ -4429,10 +4438,10 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4447,10 +4456,10 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4665,16 +4674,16 @@
         <v>81</v>
       </c>
       <c r="H21">
+        <v>96.3</v>
+      </c>
+      <c r="I21">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
         <v>92.5</v>
-      </c>
-      <c r="I21">
-        <v>97.8</v>
-      </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
-      <c r="K21">
-        <v>85</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4683,16 +4692,16 @@
         <v>81</v>
       </c>
       <c r="N21">
+        <v>96.3</v>
+      </c>
+      <c r="O21">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="P21">
+        <v>100</v>
+      </c>
+      <c r="Q21">
         <v>92.5</v>
-      </c>
-      <c r="O21">
-        <v>97.8</v>
-      </c>
-      <c r="P21">
-        <v>100</v>
-      </c>
-      <c r="Q21">
-        <v>85</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -4904,7 +4913,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4922,7 +4931,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4963,7 +4972,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4981,7 +4990,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -5196,16 +5205,16 @@
         <v>81</v>
       </c>
       <c r="H30">
+        <v>95</v>
+      </c>
+      <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
         <v>92.5</v>
-      </c>
-      <c r="I30">
-        <v>100</v>
-      </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
-      <c r="K30">
-        <v>85</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5214,16 +5223,16 @@
         <v>81</v>
       </c>
       <c r="N30">
+        <v>95</v>
+      </c>
+      <c r="O30">
+        <v>100</v>
+      </c>
+      <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
         <v>92.5</v>
-      </c>
-      <c r="O30">
-        <v>100</v>
-      </c>
-      <c r="P30">
-        <v>100</v>
-      </c>
-      <c r="Q30">
-        <v>85</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -5376,7 +5385,7 @@
         <v>97.5</v>
       </c>
       <c r="I33">
-        <v>97.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5394,7 +5403,7 @@
         <v>97.5</v>
       </c>
       <c r="O33">
-        <v>97.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5435,13 +5444,13 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5453,13 +5462,13 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5606,7 +5615,7 @@
         <v>100</v>
       </c>
       <c r="G37">
-        <v>9.5</v>
+        <v>100</v>
       </c>
       <c r="H37">
         <v>95</v>
@@ -5624,7 +5633,7 @@
         <v>100</v>
       </c>
       <c r="M37">
-        <v>9.5</v>
+        <v>100</v>
       </c>
       <c r="N37">
         <v>95</v>
@@ -5642,7 +5651,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>9.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5671,16 +5680,16 @@
         <v>90</v>
       </c>
       <c r="I38">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M38">
         <v>81</v>
@@ -5689,16 +5698,16 @@
         <v>90</v>
       </c>
       <c r="O38">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P38">
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S38">
         <v>81</v>
@@ -5730,7 +5739,7 @@
         <v>95</v>
       </c>
       <c r="I39">
-        <v>80</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -5748,7 +5757,7 @@
         <v>95</v>
       </c>
       <c r="O39">
-        <v>80</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -5817,7 +5826,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -5826,19 +5835,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>75</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>25</v>
+        <v>13.9</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5849,7 +5858,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -5858,19 +5867,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>80.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>19.4</v>
+        <v>13.9</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5881,7 +5890,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -5890,19 +5899,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5913,7 +5922,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -5922,19 +5931,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>86.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="G5" s="2">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5945,7 +5954,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -5954,19 +5963,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>86.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>13.9</v>
+        <v>5.6</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5986,19 +5995,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>94.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="G7" s="2">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6048,7 +6057,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6080,19 +6089,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920292</v>
+        <v>22330051920299</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>61</v>
@@ -6103,22 +6112,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920155</v>
+        <v>22330051920299</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
         <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6126,22 +6135,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920367</v>
+        <v>22330051920284</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6149,19 +6158,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920175</v>
+        <v>22330051920284</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
         <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
@@ -6172,24 +6181,93 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920426</v>
+        <v>22330051920150</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920153</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920157</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920426</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20231.xlsx
+++ b/grupos/3APM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -203,12 +203,12 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
@@ -230,55 +230,46 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>VICENTE</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>AVALOS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>QUINTANA</t>
   </si>
   <si>
+    <t>EDUARDO EMER</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
     <t>TONALLI</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>EDUARDO EMER</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>CRISTIAN</t>
@@ -804,7 +795,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -881,7 +872,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -958,7 +949,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1035,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1112,7 +1103,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1148,7 +1139,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1189,7 +1180,7 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1225,7 +1216,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1266,7 +1257,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1343,7 +1334,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1379,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1420,7 +1411,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1456,7 +1447,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1497,7 +1488,7 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1574,7 +1565,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1610,7 +1601,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1651,7 +1642,7 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1687,7 +1678,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1728,7 +1719,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1805,7 +1796,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1841,7 +1832,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1882,7 +1873,7 @@
         <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1918,7 +1909,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1959,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1995,7 +1986,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2036,7 +2027,7 @@
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2113,7 +2104,7 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2149,7 +2140,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2190,7 +2181,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2226,7 +2217,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2267,7 +2258,7 @@
         <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2303,7 +2294,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2344,7 +2335,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2380,7 +2371,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2421,7 +2412,7 @@
         <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2498,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2534,7 +2525,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2575,7 +2566,7 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2611,7 +2602,7 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2652,7 +2643,7 @@
         <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2729,7 +2720,7 @@
         <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2806,7 +2797,7 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2883,7 +2874,7 @@
         <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2919,7 +2910,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2960,7 +2951,7 @@
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2996,7 +2987,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3037,7 +3028,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3073,7 +3064,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3114,7 +3105,7 @@
         <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3150,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3191,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3268,7 +3259,7 @@
         <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3304,7 +3295,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3345,7 +3336,7 @@
         <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3381,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3422,7 +3413,7 @@
         <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3458,7 +3449,7 @@
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3499,7 +3490,7 @@
         <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3745,7 +3736,7 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N5">
         <v>96.3</v>
@@ -3763,7 +3754,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3922,7 +3913,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="N8">
         <v>97.5</v>
@@ -3940,7 +3931,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3981,7 +3972,7 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="N9">
         <v>91.3</v>
@@ -3999,7 +3990,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4040,7 +4031,7 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -4058,7 +4049,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4099,7 +4090,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -4117,7 +4108,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4217,7 +4208,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="N13">
         <v>93.8</v>
@@ -4235,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4276,7 +4267,7 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N14">
         <v>93.8</v>
@@ -4294,7 +4285,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4335,7 +4326,7 @@
         <v>62.5</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="N15">
         <v>92.5</v>
@@ -4353,7 +4344,7 @@
         <v>62.5</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4394,7 +4385,7 @@
         <v>50</v>
       </c>
       <c r="M16">
-        <v>81</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="N16">
         <v>66.3</v>
@@ -4412,7 +4403,7 @@
         <v>50</v>
       </c>
       <c r="S16">
-        <v>81</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4689,7 +4680,7 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>81</v>
+        <v>90.7</v>
       </c>
       <c r="N21">
         <v>96.3</v>
@@ -4707,7 +4698,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>81</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4807,7 +4798,7 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4825,7 +4816,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5220,7 +5211,7 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>81</v>
+        <v>90.7</v>
       </c>
       <c r="N30">
         <v>95</v>
@@ -5238,7 +5229,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>81</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5397,7 +5388,7 @@
         <v>100</v>
       </c>
       <c r="M33">
-        <v>100</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N33">
         <v>97.5</v>
@@ -5415,7 +5406,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5456,7 +5447,7 @@
         <v>100</v>
       </c>
       <c r="M34">
-        <v>90.5</v>
+        <v>95.3</v>
       </c>
       <c r="N34">
         <v>100</v>
@@ -5474,7 +5465,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>90.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5633,7 +5624,7 @@
         <v>100</v>
       </c>
       <c r="M37">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="N37">
         <v>95</v>
@@ -5651,7 +5642,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5692,7 +5683,7 @@
         <v>50</v>
       </c>
       <c r="M38">
-        <v>81</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="N38">
         <v>90</v>
@@ -5710,7 +5701,7 @@
         <v>50</v>
       </c>
       <c r="S38">
-        <v>81</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5751,7 +5742,7 @@
         <v>100</v>
       </c>
       <c r="M39">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="N39">
         <v>95</v>
@@ -5769,7 +5760,7 @@
         <v>100</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
   </sheetData>
@@ -5858,7 +5849,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -5879,7 +5870,7 @@
         <v>13.9</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5890,7 +5881,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -5899,19 +5890,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6057,7 +6048,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6089,19 +6080,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920299</v>
+        <v>22330051920150</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>61</v>
@@ -6112,22 +6103,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920299</v>
+        <v>22330051920153</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
         <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6135,22 +6126,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920284</v>
+        <v>22330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6158,22 +6149,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920284</v>
+        <v>22330051920299</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
         <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6181,93 +6172,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920150</v>
+        <v>22330051920426</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
         <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>62</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920153</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920157</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920426</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20231.xlsx
+++ b/grupos/3APM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -203,6 +203,9 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
@@ -212,9 +215,6 @@
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -230,49 +230,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
     <t>CERON</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>QUINTANA</t>
-  </si>
-  <si>
-    <t>EDUARDO EMER</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
+    <t>LUNA</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
+    <t>GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -798,22 +771,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -875,22 +848,22 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -902,13 +875,13 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -952,25 +925,25 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -979,7 +952,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1029,25 +1002,25 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1056,7 +1029,7 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1106,25 +1079,25 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1133,13 +1106,13 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1183,40 +1156,40 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>7</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1260,22 +1233,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1337,37 +1310,37 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>8</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>10</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1414,25 +1387,25 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1441,13 +1414,13 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1491,22 +1464,22 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1518,13 +1491,13 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1568,28 +1541,28 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>8</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1601,7 +1574,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1645,22 +1618,22 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1672,7 +1645,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1722,22 +1695,22 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1799,34 +1772,34 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -1876,22 +1849,22 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -1903,10 +1876,10 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -1953,22 +1926,22 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -1980,10 +1953,10 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2030,25 +2003,25 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2107,40 +2080,40 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2184,22 +2157,22 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2211,13 +2184,13 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2261,22 +2234,22 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2285,10 +2258,10 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2338,22 +2311,22 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2365,7 +2338,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2415,34 +2388,34 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2492,28 +2465,28 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2569,22 +2542,22 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2593,16 +2566,16 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2646,34 +2619,34 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>10</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2723,22 +2696,22 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2750,7 +2723,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -2800,40 +2773,40 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>6</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2877,25 +2850,25 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -2904,10 +2877,10 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -2954,22 +2927,22 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -2987,7 +2960,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3031,25 +3004,25 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3108,31 +3081,31 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3185,28 +3158,28 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>9</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3262,37 +3235,37 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>8</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3339,22 +3312,22 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>7</v>
@@ -3416,31 +3389,31 @@
         <v>5</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3493,40 +3466,40 @@
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
         <v>7</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3739,22 +3712,22 @@
         <v>86</v>
       </c>
       <c r="N5">
-        <v>96.3</v>
+        <v>94.5</v>
       </c>
       <c r="O5">
-        <v>88.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>95</v>
+        <v>88.3</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>86</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3798,7 +3771,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3857,7 +3830,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3916,7 +3889,7 @@
         <v>90.7</v>
       </c>
       <c r="N8">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -3931,7 +3904,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>90.7</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3975,7 +3948,7 @@
         <v>93</v>
       </c>
       <c r="N9">
-        <v>91.3</v>
+        <v>93.8</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3984,13 +3957,13 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="R9">
         <v>100</v>
       </c>
       <c r="S9">
-        <v>93</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4049,7 +4022,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4108,7 +4081,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>93</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4152,7 +4125,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4211,22 +4184,22 @@
         <v>93</v>
       </c>
       <c r="N13">
-        <v>93.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O13">
-        <v>97.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>93</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4270,22 +4243,22 @@
         <v>88.40000000000001</v>
       </c>
       <c r="N14">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="O14">
         <v>93.8</v>
       </c>
-      <c r="O14">
-        <v>90</v>
-      </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>88.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4329,22 +4302,22 @@
         <v>86</v>
       </c>
       <c r="N15">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="O15">
-        <v>93.3</v>
+        <v>88.2</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="R15">
-        <v>62.5</v>
+        <v>58.3</v>
       </c>
       <c r="S15">
-        <v>86</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4388,22 +4361,22 @@
         <v>67.40000000000001</v>
       </c>
       <c r="N16">
-        <v>66.3</v>
+        <v>55.5</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P16">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="Q16">
-        <v>40</v>
+        <v>26.7</v>
       </c>
       <c r="R16">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="S16">
-        <v>67.40000000000001</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4447,22 +4420,22 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="O17">
-        <v>97.8</v>
+        <v>95.8</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4683,22 +4656,22 @@
         <v>90.7</v>
       </c>
       <c r="N21">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O21">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>90.7</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4757,7 +4730,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4816,7 +4789,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4922,7 +4895,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4981,7 +4954,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -5037,10 +5010,10 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O27">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -5052,7 +5025,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5214,22 +5187,22 @@
         <v>90.7</v>
       </c>
       <c r="N30">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O30">
+        <v>100</v>
+      </c>
+      <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
         <v>95</v>
       </c>
-      <c r="O30">
-        <v>100</v>
-      </c>
-      <c r="P30">
-        <v>100</v>
-      </c>
-      <c r="Q30">
-        <v>92.5</v>
-      </c>
       <c r="R30">
         <v>100</v>
       </c>
       <c r="S30">
-        <v>90.7</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5335,7 +5308,7 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -5391,10 +5364,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="N33">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O33">
-        <v>95.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5406,7 +5379,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>88.40000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5450,22 +5423,22 @@
         <v>95.3</v>
       </c>
       <c r="N34">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O34">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>95.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5583,7 +5556,7 @@
         <v>100</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5627,10 +5600,10 @@
         <v>95.3</v>
       </c>
       <c r="N37">
-        <v>95</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O37">
-        <v>95.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -5642,7 +5615,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>95.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5686,22 +5659,22 @@
         <v>67.40000000000001</v>
       </c>
       <c r="N38">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="O38">
-        <v>94.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P38">
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>95</v>
+        <v>63.3</v>
       </c>
       <c r="R38">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="S38">
-        <v>67.40000000000001</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5745,22 +5718,22 @@
         <v>95.3</v>
       </c>
       <c r="N39">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O39">
+        <v>91.7</v>
+      </c>
+      <c r="P39">
+        <v>100</v>
+      </c>
+      <c r="Q39">
         <v>95</v>
       </c>
-      <c r="O39">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="P39">
-        <v>100</v>
-      </c>
-      <c r="Q39">
-        <v>100</v>
-      </c>
       <c r="R39">
         <v>100</v>
       </c>
       <c r="S39">
-        <v>95.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5826,19 +5799,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5849,7 +5822,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -5858,19 +5831,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>86.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="G3" s="2">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5881,7 +5854,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -5890,19 +5863,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>86.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="G4" s="2">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5913,7 +5886,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -5922,19 +5895,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5945,7 +5918,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -5966,7 +5939,7 @@
         <v>5.6</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6048,7 +6021,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6080,22 +6053,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920150</v>
+        <v>22330051920157</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6103,93 +6076,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920153</v>
+        <v>22330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920157</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920299</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920426</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20231.xlsx
+++ b/grupos/3APM - Estadisticos 20231.xlsx
@@ -866,22 +866,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -943,22 +943,22 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1020,22 +1020,22 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>10</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1097,22 +1097,22 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1174,22 +1174,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1251,16 +1251,16 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1328,22 +1328,22 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1405,22 +1405,22 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>10</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1482,22 +1482,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1559,22 +1559,22 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1642,10 +1642,10 @@
         <v>5</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1790,22 +1790,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1867,22 +1867,22 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>10</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1944,22 +1944,22 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>10</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2021,19 +2021,19 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2098,22 +2098,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2175,22 +2175,22 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2252,22 +2252,22 @@
         <v>9</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2329,22 +2329,22 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2406,22 +2406,22 @@
         <v>10</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2483,22 +2483,22 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>10</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2560,22 +2560,22 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2637,19 +2637,19 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2714,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -2723,10 +2723,10 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -2791,22 +2791,22 @@
         <v>8</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>5</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2868,22 +2868,22 @@
         <v>8</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2945,22 +2945,22 @@
         <v>10</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>10</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3022,22 +3022,22 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3099,22 +3099,22 @@
         <v>9</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3176,16 +3176,16 @@
         <v>10</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3253,22 +3253,22 @@
         <v>9</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3330,22 +3330,22 @@
         <v>10</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3407,13 +3407,13 @@
         <v>5</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3484,22 +3484,22 @@
         <v>9</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5811,7 +5811,7 @@
         <v>11.1</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5843,7 +5843,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5875,7 +5875,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5907,7 +5907,7 @@
         <v>5.6</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>5.6</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5971,7 +5971,7 @@
         <v>2.8</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3APM - Estadisticos 20231.xlsx
+++ b/grupos/3APM - Estadisticos 20231.xlsx
@@ -866,22 +866,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -943,22 +943,22 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1020,22 +1020,22 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>10</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1097,22 +1097,22 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1174,22 +1174,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1251,16 +1251,16 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1328,22 +1328,22 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>10</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1405,22 +1405,22 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>10</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1482,22 +1482,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1559,22 +1559,22 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1642,10 +1642,10 @@
         <v>5</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1790,22 +1790,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1867,22 +1867,22 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>10</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1944,22 +1944,22 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>10</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2021,19 +2021,19 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>10</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2098,22 +2098,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2175,22 +2175,22 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2252,22 +2252,22 @@
         <v>9</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2329,22 +2329,22 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>10</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2406,22 +2406,22 @@
         <v>10</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2483,22 +2483,22 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>10</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2560,22 +2560,22 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2637,19 +2637,19 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>10</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2714,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -2723,10 +2723,10 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -2791,22 +2791,22 @@
         <v>8</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>5</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2868,22 +2868,22 @@
         <v>8</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2945,22 +2945,22 @@
         <v>10</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>10</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3022,22 +3022,22 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3099,22 +3099,22 @@
         <v>9</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3176,16 +3176,16 @@
         <v>10</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>10</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3253,22 +3253,22 @@
         <v>9</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3330,22 +3330,22 @@
         <v>10</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3407,13 +3407,13 @@
         <v>5</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3484,22 +3484,22 @@
         <v>9</v>
       </c>
       <c r="T39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y39">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5811,7 +5811,7 @@
         <v>11.1</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5843,7 +5843,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5875,7 +5875,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5907,7 +5907,7 @@
         <v>5.6</v>
       </c>
       <c r="H5">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>5.6</v>
       </c>
       <c r="H6">
-        <v>9.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5971,7 +5971,7 @@
         <v>2.8</v>
       </c>
       <c r="H7">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
